--- a/results/CRISPR/crispr_multivariate_results.xlsx
+++ b/results/CRISPR/crispr_multivariate_results.xlsx
@@ -409,19 +409,19 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>2.352564796379433</v>
+        <v>2.352564796379436</v>
       </c>
       <c r="D2">
-        <v>0.1668741866827253</v>
+        <v>0.1668741866827249</v>
       </c>
       <c r="E2">
-        <v>0.04919498370509615</v>
+        <v>0.04919498370509653</v>
       </c>
       <c r="F2">
-        <v>0.5773537167338281</v>
+        <v>0.5773537167338251</v>
       </c>
       <c r="G2">
-        <v>-0.000430276820348352</v>
+        <v>-0.0004302768203487961</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -432,16 +432,16 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.8754353000483068</v>
+        <v>0.8754353000483069</v>
       </c>
       <c r="D3">
-        <v>0.3131186506050661</v>
+        <v>0.3131186506050662</v>
       </c>
       <c r="E3">
-        <v>-0.01639826553678041</v>
+        <v>-0.01639826553678039</v>
       </c>
       <c r="F3">
-        <v>0.7164746897883244</v>
+        <v>0.7164746897883246</v>
       </c>
       <c r="G3">
         <v>-0.00708371020240417</v>
@@ -455,19 +455,19 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.4521090163395226</v>
+        <v>0.4521090163395228</v>
       </c>
       <c r="D4">
-        <v>0.4419454643407814</v>
+        <v>0.4419454643407813</v>
       </c>
       <c r="E4">
-        <v>0.02372605811668001</v>
+        <v>0.02372605811668002</v>
       </c>
       <c r="F4">
-        <v>0.4396710640341315</v>
+        <v>0.4396710640341311</v>
       </c>
       <c r="G4">
-        <v>-0.01752004017163755</v>
+        <v>-0.01752004017163777</v>
       </c>
     </row>
   </sheetData>

--- a/results/CRISPR/crispr_multivariate_results.xlsx
+++ b/results/CRISPR/crispr_multivariate_results.xlsx
@@ -409,16 +409,16 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>2.352564796379436</v>
+        <v>2.35256479637944</v>
       </c>
       <c r="D2">
-        <v>0.1668741866827249</v>
+        <v>0.1668741866827244</v>
       </c>
       <c r="E2">
-        <v>0.04919498370509653</v>
+        <v>0.04919498370509637</v>
       </c>
       <c r="F2">
-        <v>0.5773537167338251</v>
+        <v>0.5773537167338262</v>
       </c>
       <c r="G2">
         <v>-0.0004302768203487961</v>
@@ -432,13 +432,13 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.8754353000483069</v>
+        <v>0.8754353000483078</v>
       </c>
       <c r="D3">
-        <v>0.3131186506050662</v>
+        <v>0.3131186506050659</v>
       </c>
       <c r="E3">
-        <v>-0.01639826553678039</v>
+        <v>-0.01639826553678038</v>
       </c>
       <c r="F3">
         <v>0.7164746897883246</v>
@@ -455,13 +455,13 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.4521090163395228</v>
+        <v>0.4521090163395231</v>
       </c>
       <c r="D4">
-        <v>0.4419454643407813</v>
+        <v>0.4419454643407812</v>
       </c>
       <c r="E4">
-        <v>0.02372605811668002</v>
+        <v>0.02372605811668001</v>
       </c>
       <c r="F4">
         <v>0.4396710640341311</v>

--- a/results/CRISPR/crispr_multivariate_results.xlsx
+++ b/results/CRISPR/crispr_multivariate_results.xlsx
@@ -409,16 +409,16 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>2.35256479637944</v>
+        <v>2.352564796379433</v>
       </c>
       <c r="D2">
-        <v>0.1668741866827244</v>
+        <v>0.1668741866827253</v>
       </c>
       <c r="E2">
-        <v>0.04919498370509637</v>
+        <v>0.04919498370509565</v>
       </c>
       <c r="F2">
-        <v>0.5773537167338262</v>
+        <v>0.5773537167338317</v>
       </c>
       <c r="G2">
         <v>-0.0004302768203487961</v>
@@ -432,16 +432,16 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.8754353000483078</v>
+        <v>0.8754353000483065</v>
       </c>
       <c r="D3">
-        <v>0.3131186506050659</v>
+        <v>0.3131186506050663</v>
       </c>
       <c r="E3">
-        <v>-0.01639826553678038</v>
+        <v>-0.01639826553678044</v>
       </c>
       <c r="F3">
-        <v>0.7164746897883246</v>
+        <v>0.7164746897883235</v>
       </c>
       <c r="G3">
         <v>-0.00708371020240417</v>
@@ -455,16 +455,16 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.4521090163395231</v>
+        <v>0.4521090163395224</v>
       </c>
       <c r="D4">
-        <v>0.4419454643407812</v>
+        <v>0.4419454643407817</v>
       </c>
       <c r="E4">
-        <v>0.02372605811668001</v>
+        <v>0.02372605811667993</v>
       </c>
       <c r="F4">
-        <v>0.4396710640341311</v>
+        <v>0.4396710640341325</v>
       </c>
       <c r="G4">
         <v>-0.01752004017163777</v>

--- a/results/CRISPR/crispr_multivariate_results.xlsx
+++ b/results/CRISPR/crispr_multivariate_results.xlsx
@@ -409,19 +409,19 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>2.352564796379433</v>
+        <v>2.352564796379439</v>
       </c>
       <c r="D2">
-        <v>0.1668741866827253</v>
+        <v>0.1668741866827246</v>
       </c>
       <c r="E2">
-        <v>0.04919498370509565</v>
+        <v>0.04919498370509603</v>
       </c>
       <c r="F2">
-        <v>0.5773537167338317</v>
+        <v>0.5773537167338288</v>
       </c>
       <c r="G2">
-        <v>-0.0004302768203487961</v>
+        <v>-0.000430276820348352</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -432,19 +432,19 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.8754353000483065</v>
+        <v>0.8754353000483069</v>
       </c>
       <c r="D3">
-        <v>0.3131186506050663</v>
+        <v>0.3131186506050664</v>
       </c>
       <c r="E3">
-        <v>-0.01639826553678044</v>
+        <v>-0.0163982655367804</v>
       </c>
       <c r="F3">
-        <v>0.7164746897883235</v>
+        <v>0.7164746897883244</v>
       </c>
       <c r="G3">
-        <v>-0.00708371020240417</v>
+        <v>-0.007083710202404392</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -455,19 +455,19 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.4521090163395224</v>
+        <v>0.4521090163395226</v>
       </c>
       <c r="D4">
-        <v>0.4419454643407817</v>
+        <v>0.441945464340782</v>
       </c>
       <c r="E4">
-        <v>0.02372605811667993</v>
+        <v>0.02372605811667997</v>
       </c>
       <c r="F4">
-        <v>0.4396710640341325</v>
+        <v>0.4396710640341321</v>
       </c>
       <c r="G4">
-        <v>-0.01752004017163777</v>
+        <v>-0.01752004017163755</v>
       </c>
     </row>
   </sheetData>

--- a/results/CRISPR/crispr_multivariate_results.xlsx
+++ b/results/CRISPR/crispr_multivariate_results.xlsx
@@ -409,7 +409,7 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>2.352564796379439</v>
+        <v>2.352564796379438</v>
       </c>
       <c r="D2">
         <v>0.1668741866827246</v>
@@ -421,7 +421,7 @@
         <v>0.5773537167338288</v>
       </c>
       <c r="G2">
-        <v>-0.000430276820348352</v>
+        <v>-0.0004302768203487961</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -432,19 +432,19 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>0.8754353000483069</v>
+        <v>0.8754353000483071</v>
       </c>
       <c r="D3">
-        <v>0.3131186506050664</v>
+        <v>0.3131186506050661</v>
       </c>
       <c r="E3">
         <v>-0.0163982655367804</v>
       </c>
       <c r="F3">
-        <v>0.7164746897883244</v>
+        <v>0.7164746897883242</v>
       </c>
       <c r="G3">
-        <v>-0.007083710202404392</v>
+        <v>-0.00708371020240417</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -455,19 +455,19 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.4521090163395226</v>
+        <v>0.4521090163395228</v>
       </c>
       <c r="D4">
-        <v>0.441945464340782</v>
+        <v>0.4419454643407813</v>
       </c>
       <c r="E4">
-        <v>0.02372605811667997</v>
+        <v>0.02372605811667999</v>
       </c>
       <c r="F4">
-        <v>0.4396710640341321</v>
+        <v>0.4396710640341315</v>
       </c>
       <c r="G4">
-        <v>-0.01752004017163755</v>
+        <v>-0.01752004017163777</v>
       </c>
     </row>
   </sheetData>

--- a/results/CRISPR/crispr_multivariate_results.xlsx
+++ b/results/CRISPR/crispr_multivariate_results.xlsx
@@ -409,16 +409,16 @@
         <v>64</v>
       </c>
       <c r="C2">
-        <v>2.352564796379438</v>
+        <v>2.352564796379434</v>
       </c>
       <c r="D2">
-        <v>0.1668741866827246</v>
+        <v>0.1668741866827253</v>
       </c>
       <c r="E2">
-        <v>0.04919498370509603</v>
+        <v>0.04919498370509584</v>
       </c>
       <c r="F2">
-        <v>0.5773537167338288</v>
+        <v>0.5773537167338304</v>
       </c>
       <c r="G2">
         <v>-0.0004302768203487961</v>
@@ -438,10 +438,10 @@
         <v>0.3131186506050661</v>
       </c>
       <c r="E3">
-        <v>-0.0163982655367804</v>
+        <v>-0.01639826553678042</v>
       </c>
       <c r="F3">
-        <v>0.7164746897883242</v>
+        <v>0.716474689788324</v>
       </c>
       <c r="G3">
         <v>-0.00708371020240417</v>
@@ -455,19 +455,19 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.4521090163395228</v>
+        <v>0.4521090163395227</v>
       </c>
       <c r="D4">
-        <v>0.4419454643407813</v>
+        <v>0.4419454643407814</v>
       </c>
       <c r="E4">
-        <v>0.02372605811667999</v>
+        <v>0.02372605811667997</v>
       </c>
       <c r="F4">
-        <v>0.4396710640341315</v>
+        <v>0.4396710640341321</v>
       </c>
       <c r="G4">
-        <v>-0.01752004017163777</v>
+        <v>-0.01752004017163755</v>
       </c>
     </row>
   </sheetData>
